--- a/rosnedra_forecast/2026/rosnedra_page14.xlsx
+++ b/rosnedra_forecast/2026/rosnedra_page14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -443,13 +443,13 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Извлекаемые запасы и природные ресурсы (с указанием категории) (ед.изм)</t>
+          <t>Извлекаемые запасы и прогнозные ресурсы</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -458,21 +458,24 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Харасавэйский</t>
+          <t>Верхнехарловский</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>газ (извл.)
-C1 - 247,3 млрд м3
-конденсат (извл.)
-C1 - 15,4 млн т</t>
+          <t>нефть (извл.):
+C1 - 0,380 млн.т;
+C2 - 7,119 млн.т;
+D0 - 8,199 млн.т;
+газ(извл.):
+C1 - 0,038 млрд.м3;
+C2 - 0,767 млрд.м3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
@@ -481,21 +484,21 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Крузенштернский</t>
+          <t>Апакопурский</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>газ (извл.)
-C1 - 186,2 млрд м3
-конденсат (извл.)
-C1 - 11,8 млн т</t>
+          <t>нефть (извл.):
+C1 - 0,644 млн.т
+C2 - 1,218 млн.т;
+Dл - 0,433 млн.т;</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -504,21 +507,23 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Ленинградский</t>
+          <t>Северо-Крещенский</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>газ (извл.)
-C1 - 321,5 млрд м3
-конденсат (извл.)
-C1 - 18,9 млн т</t>
+          <t>нефть (извл.):
+D1 - 3,283 млн.т;
+газ (извл.):
+D1 - 4,801 млрд.м3
+конденсат (извл.):
+D1 - 0,375 млн.т</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
@@ -527,38 +532,16 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Русановский</t>
+          <t>Западно-Заполярный</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>газ (извл.)
-C1 - 402,7 млрд м3
-конденсат (извл.)
-C1 - 24,1 млн т</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Ямало-Ненецкий автономный округ</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Каменномысский</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>газ (извл.)
-C1 - 156,9 млрд м3
-конденсат (извл.)
-C1 - 9,6 млн т</t>
+          <t>нефть (извл.):
+D0 - 6,200 млн.т;
+газ(извл.):
+C1 - 3,068 млрд.м3;
+D0 - 41,121 млрд.м3</t>
         </is>
       </c>
     </row>
